--- a/5/search/FY3_Missile3_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY3_Missile3_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,37 +492,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>119.9</v>
+        <v>125.4</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>6393.32781047969</v>
+        <v>6525.93898556384</v>
       </c>
       <c r="F2" t="n">
-        <v>-270.4940880255899</v>
+        <v>-189.6698845395263</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6410.429019630981</v>
+        <v>6535.165985310574</v>
       </c>
       <c r="I2" t="n">
-        <v>-151.819917939746</v>
+        <v>-140.3658474261848</v>
       </c>
       <c r="J2" t="n">
-        <v>695.1</v>
+        <v>699.216</v>
       </c>
       <c r="K2" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -530,37 +530,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="B3" t="n">
-        <v>131.3</v>
+        <v>128.8</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>21.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
-        <v>6104.467193358235</v>
+        <v>6380.020502557516</v>
       </c>
       <c r="F3" t="n">
-        <v>-507.4882757523778</v>
+        <v>-296.0136222170172</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6120.962013362167</v>
+        <v>6401.531097041904</v>
       </c>
       <c r="I3" t="n">
-        <v>-113.9337929764375</v>
+        <v>-142.9577895123201</v>
       </c>
       <c r="J3" t="n">
-        <v>655.9</v>
+        <v>692.944</v>
       </c>
       <c r="K3" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -568,75 +568,75 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80.2</v>
+        <v>82</v>
       </c>
       <c r="B4" t="n">
-        <v>121.9</v>
+        <v>126.8</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>21.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
-        <v>6477.216372811806</v>
+        <v>6374.11956307681</v>
       </c>
       <c r="F4" t="n">
-        <v>-237.2118750218388</v>
+        <v>-338.0009883316602</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6493.815203170478</v>
+        <v>6402.355001799588</v>
       </c>
       <c r="I4" t="n">
-        <v>-141.1148967617287</v>
+        <v>-137.0954025453702</v>
       </c>
       <c r="J4" t="n">
-        <v>696.864</v>
+        <v>687.456</v>
       </c>
       <c r="K4" t="n">
-        <v>2.899999999999999</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="B5" t="n">
-        <v>120.9</v>
+        <v>122.4</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>6473.301554330987</v>
+        <v>6340.514950055624</v>
       </c>
       <c r="F5" t="n">
-        <v>-259.8762566869591</v>
+        <v>-378.1801140450902</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6493.87988278016</v>
+        <v>6372.044112097811</v>
       </c>
       <c r="I5" t="n">
-        <v>-140.7404417603051</v>
+        <v>-135.4190134937097</v>
       </c>
       <c r="J5" t="n">
-        <v>695.1</v>
+        <v>680.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.899999999999999</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
@@ -644,37 +644,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="B6" t="n">
-        <v>118.9</v>
+        <v>123.4</v>
       </c>
       <c r="C6" t="n">
-        <v>23.4</v>
+        <v>21.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
-        <v>6473.567081149686</v>
+        <v>6343.296934941699</v>
       </c>
       <c r="F6" t="n">
-        <v>-258.3390203653248</v>
+        <v>-356.7600169376155</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>6493.804990600527</v>
+        <v>6371.905012853507</v>
       </c>
       <c r="I6" t="n">
-        <v>-141.1740212356378</v>
+        <v>-136.4900183490834</v>
       </c>
       <c r="J6" t="n">
-        <v>695.1</v>
+        <v>684.124</v>
       </c>
       <c r="K6" t="n">
-        <v>2.899999999999999</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -682,37 +682,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86</v>
+        <v>86.8</v>
       </c>
       <c r="B7" t="n">
-        <v>126.3</v>
+        <v>129.8</v>
       </c>
       <c r="C7" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E7" t="n">
-        <v>6177.966901204437</v>
+        <v>6140.565248153386</v>
       </c>
       <c r="F7" t="n">
-        <v>-454.9547411341209</v>
+        <v>-485.8063428980699</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>6200.873532052533</v>
+        <v>6160.853015928102</v>
       </c>
       <c r="I7" t="n">
-        <v>-127.3746583097997</v>
+        <v>-122.9330315637707</v>
       </c>
       <c r="J7" t="n">
-        <v>666.876</v>
+        <v>661.5839999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>2.899999999999999</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
@@ -720,75 +720,75 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="B8" t="n">
-        <v>117.9</v>
+        <v>132.8</v>
       </c>
       <c r="C8" t="n">
-        <v>23.4</v>
+        <v>18.2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="E8" t="n">
-        <v>6393.493260042788</v>
+        <v>5932.514516070683</v>
       </c>
       <c r="F8" t="n">
-        <v>-269.3459475977374</v>
+        <v>-583.982336352065</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>6410.309211326668</v>
+        <v>5919.16573902972</v>
       </c>
       <c r="I8" t="n">
-        <v>-152.6513299737091</v>
+        <v>-106.0887325535721</v>
       </c>
       <c r="J8" t="n">
-        <v>695.1</v>
+        <v>636.496</v>
       </c>
       <c r="K8" t="n">
-        <v>2.800000000000001</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>81.8</v>
+        <v>81</v>
       </c>
       <c r="B9" t="n">
-        <v>122.9</v>
+        <v>123.4</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>6403.16920690537</v>
+        <v>6440.131496079991</v>
       </c>
       <c r="F9" t="n">
-        <v>-202.1995280929527</v>
+        <v>-221.1190999687678</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>6410.180845286332</v>
+        <v>6451.71390387157</v>
       </c>
       <c r="I9" t="n">
-        <v>-153.542128581526</v>
+        <v>-147.9906552311037</v>
       </c>
       <c r="J9" t="n">
-        <v>699.216</v>
+        <v>698.236</v>
       </c>
       <c r="K9" t="n">
-        <v>2.800000000000001</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L9" t="n">
         <v>3</v>
@@ -796,37 +796,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>81.8</v>
+        <v>81</v>
       </c>
       <c r="B10" t="n">
-        <v>120.9</v>
+        <v>124.4</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>6396.608275954916</v>
+        <v>6443.698201882908</v>
       </c>
       <c r="F10" t="n">
-        <v>-247.7292347147113</v>
+        <v>-198.5998058031987</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>6410.403346422913</v>
+        <v>6451.482380863309</v>
       </c>
       <c r="I10" t="n">
-        <v>-151.9980776613099</v>
+        <v>-149.4524339751848</v>
       </c>
       <c r="J10" t="n">
-        <v>696.864</v>
+        <v>699.216</v>
       </c>
       <c r="K10" t="n">
-        <v>2.800000000000001</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -834,40 +834,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="B11" t="n">
-        <v>128.3</v>
+        <v>116.4</v>
       </c>
       <c r="C11" t="n">
-        <v>19.4</v>
+        <v>22.8</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>6034.752146107739</v>
+        <v>6341.813209669125</v>
       </c>
       <c r="F11" t="n">
-        <v>-511.2226196903616</v>
+        <v>-368.1840687282684</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>6040.126189320276</v>
+        <v>6371.796824552382</v>
       </c>
       <c r="I11" t="n">
-        <v>-126.3601381991804</v>
+        <v>-137.3230221254849</v>
       </c>
       <c r="J11" t="n">
-        <v>655.9</v>
+        <v>680.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.800000000000001</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/FY3_Missile3_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY3_Missile3_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,268 +492,268 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="B2" t="n">
-        <v>125.4</v>
+        <v>135.4</v>
       </c>
       <c r="C2" t="n">
-        <v>22.8</v>
+        <v>19.6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="E2" t="n">
-        <v>6525.93898556384</v>
+        <v>6355.577898310481</v>
       </c>
       <c r="F2" t="n">
-        <v>-189.6698845395263</v>
+        <v>-370.0891452687783</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6535.165985310574</v>
+        <v>6388.233011420627</v>
       </c>
       <c r="I2" t="n">
-        <v>-140.3658474261848</v>
+        <v>-128.5667198342783</v>
       </c>
       <c r="J2" t="n">
-        <v>699.216</v>
+        <v>684.124</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>3.100000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>128.8</v>
+        <v>135.2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.2</v>
+        <v>19.4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>6380.020502557516</v>
+        <v>6315.104511842619</v>
       </c>
       <c r="F3" t="n">
-        <v>-296.0136222170172</v>
+        <v>-396.1166230000963</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6401.531097041904</v>
+        <v>6347.589513063508</v>
       </c>
       <c r="I3" t="n">
-        <v>-142.9577895123201</v>
+        <v>-127.6750377423742</v>
       </c>
       <c r="J3" t="n">
-        <v>692.944</v>
+        <v>680.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.100000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="B4" t="n">
-        <v>126.8</v>
+        <v>137.4</v>
       </c>
       <c r="C4" t="n">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>6374.11956307681</v>
+        <v>6525.718243943105</v>
       </c>
       <c r="F4" t="n">
-        <v>-338.0009883316602</v>
+        <v>-190.8494069585058</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6402.355001799588</v>
+        <v>6535.82821017278</v>
       </c>
       <c r="I4" t="n">
-        <v>-137.0954025453702</v>
+        <v>-136.8272801692465</v>
       </c>
       <c r="J4" t="n">
-        <v>687.456</v>
+        <v>699.216</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>3.100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="B5" t="n">
-        <v>122.4</v>
+        <v>138.8</v>
       </c>
       <c r="C5" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="D5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6525.968417779938</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-189.5126148836616</v>
+      </c>
+      <c r="G5" t="n">
+        <v>700</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6536.181396765956</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-134.9400442988785</v>
+      </c>
+      <c r="J5" t="n">
+        <v>699.216</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.100000000000001</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6340.514950055624</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-378.1801140450902</v>
-      </c>
-      <c r="G5" t="n">
-        <v>700</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6372.044112097811</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-135.4190134937097</v>
-      </c>
-      <c r="J5" t="n">
-        <v>680.4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="B6" t="n">
-        <v>123.4</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="E6" t="n">
-        <v>6343.296934941699</v>
+        <v>6424.34412986813</v>
       </c>
       <c r="F6" t="n">
-        <v>-356.7600169376155</v>
+        <v>-320.7966073016291</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>6371.905012853507</v>
+        <v>6454.348260262846</v>
       </c>
       <c r="I6" t="n">
-        <v>-136.4900183490834</v>
+        <v>-131.3579835754819</v>
       </c>
       <c r="J6" t="n">
-        <v>684.124</v>
+        <v>690.3960000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.100000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86.8</v>
+        <v>80.2</v>
       </c>
       <c r="B7" t="n">
-        <v>129.8</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>6140.565248153386</v>
+        <v>6485.028988823527</v>
       </c>
       <c r="F7" t="n">
-        <v>-485.8063428980699</v>
+        <v>-191.9816524814469</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>6160.853015928102</v>
+        <v>6494.356469377825</v>
       </c>
       <c r="I7" t="n">
-        <v>-122.9330315637707</v>
+        <v>-137.9812996445518</v>
       </c>
       <c r="J7" t="n">
-        <v>661.5839999999999</v>
+        <v>699.216</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>3.100000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="B8" t="n">
-        <v>132.8</v>
+        <v>138.4</v>
       </c>
       <c r="C8" t="n">
-        <v>18.2</v>
+        <v>20.4</v>
       </c>
       <c r="D8" t="n">
-        <v>3.6</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>5932.514516070683</v>
+        <v>6480.56269156541</v>
       </c>
       <c r="F8" t="n">
-        <v>-583.982336352065</v>
+        <v>-217.8387557376532</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>5919.16573902972</v>
+        <v>6494.696888376157</v>
       </c>
       <c r="I8" t="n">
-        <v>-106.0887325535721</v>
+        <v>-136.0104838475839</v>
       </c>
       <c r="J8" t="n">
-        <v>636.496</v>
+        <v>698.236</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>3.099999999999998</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -761,113 +761,113 @@
         <v>81</v>
       </c>
       <c r="B9" t="n">
-        <v>123.4</v>
+        <v>138.2</v>
       </c>
       <c r="C9" t="n">
-        <v>22.8</v>
+        <v>19.8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
-        <v>6440.131496079991</v>
+        <v>6428.061012757486</v>
       </c>
       <c r="F9" t="n">
-        <v>-221.1190999687678</v>
+        <v>-297.3291323290891</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>6451.71390387157</v>
+        <v>6454.004104439759</v>
       </c>
       <c r="I9" t="n">
-        <v>-147.9906552311037</v>
+        <v>-133.5308979247916</v>
       </c>
       <c r="J9" t="n">
-        <v>698.236</v>
+        <v>692.944</v>
       </c>
       <c r="K9" t="n">
-        <v>2.900000000000002</v>
+        <v>3.099999999999998</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>81</v>
+        <v>80.2</v>
       </c>
       <c r="B10" t="n">
-        <v>124.4</v>
+        <v>138.6</v>
       </c>
       <c r="C10" t="n">
-        <v>22.8</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>6443.698201882908</v>
+        <v>6471.820731688243</v>
       </c>
       <c r="F10" t="n">
-        <v>-198.5998058031987</v>
+        <v>-268.4493054037653</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>6451.482380863309</v>
+        <v>6495.411768272655</v>
       </c>
       <c r="I10" t="n">
-        <v>-149.4524339751848</v>
+        <v>-131.8717706739535</v>
       </c>
       <c r="J10" t="n">
-        <v>699.216</v>
+        <v>695.1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.900000000000002</v>
+        <v>3.099999999999998</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>82.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="B11" t="n">
-        <v>116.4</v>
+        <v>137.2</v>
       </c>
       <c r="C11" t="n">
-        <v>22.8</v>
+        <v>20.4</v>
       </c>
       <c r="D11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6476.395963025825</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-241.9615410925298</v>
+      </c>
+      <c r="G11" t="n">
+        <v>700</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6495.078157654289</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-133.8031701549819</v>
+      </c>
+      <c r="J11" t="n">
+        <v>696.864</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.099999999999998</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>6341.813209669125</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-368.1840687282684</v>
-      </c>
-      <c r="G11" t="n">
-        <v>700</v>
-      </c>
-      <c r="H11" t="n">
-        <v>6371.796824552382</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-137.3230221254849</v>
-      </c>
-      <c r="J11" t="n">
-        <v>680.4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.900000000000002</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
